--- a/iter-v1.0.1-第二期/测试用例.xlsx
+++ b/iter-v1.0.1-第二期/测试用例.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\work\cn_app_plus\iter-v1.0.1-第二期\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cjsj_release\snooker_master_app\iter-v1.0.1-第二期\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12780"/>
+    <workbookView windowWidth="28800" windowHeight="12900"/>
   </bookViews>
   <sheets>
     <sheet name="安卓" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="冒烟测试" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">安卓!$A$1:$O$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">安卓!$A$1:$O$163</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4190" uniqueCount="1348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4552" uniqueCount="1416">
   <si>
     <t>用例编号</t>
   </si>
@@ -3680,6 +3680,230 @@
 3.底图与设计稿一致</t>
   </si>
   <si>
+    <t>Bug转测试用例（第二期）</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0149</t>
+  </si>
+  <si>
+    <t>App评级显示称号和数据一致性</t>
+  </si>
+  <si>
+    <t>App评级页面正确显示称号且评级数据与小程序一致</t>
+  </si>
+  <si>
+    <t>用户在小程序端已有评级数据（如防守专家称号），App已登录同一账号</t>
+  </si>
+  <si>
+    <t>1.在小程序查看排行榜评级信息，记录称号和数据
+2.打开App登录同一账号
+3.进入【我的数据】页面
+4.查看评级卡片称号
+5.查看评级数值和五维雷达图数据
+6.对比App与小程序的评级数据</t>
+  </si>
+  <si>
+    <t>1.App评级卡片正确显示称号（如防守专家）
+2.评级数值与小程序一致
+3.五维雷达图数据与小程序一致
+4.App与小程序评级称号和数据完全同步</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0150</t>
+  </si>
+  <si>
+    <t>场详情模块</t>
+  </si>
+  <si>
+    <t>场详情页面底部遮罩</t>
+  </si>
+  <si>
+    <t>场详情页面底部无异常遮罩遮挡内容</t>
+  </si>
+  <si>
+    <t>用户已登录App，存在可查看的场次</t>
+  </si>
+  <si>
+    <t>1.进入比赛记录或场次列表
+2.点击任一场次进入场详情页
+3.上下滑动页面查看各tab内容
+4.重点查看页面底部区域
+5.检查是否有遮罩层覆盖页面内容</t>
+  </si>
+  <si>
+    <t>1.场详情页正常打开
+2.页面各区域内容完整展示
+3.页面底部无异常遮罩层
+4.底部按钮和操作区域可正常点击</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0151</t>
+  </si>
+  <si>
+    <t>斯诺克大师国内APP、斯诺克大师小程序</t>
+  </si>
+  <si>
+    <t>App排行榜评级数据与小程序同步</t>
+  </si>
+  <si>
+    <t>App排行榜评级数据与小程序一致，不显示数据不足</t>
+  </si>
+  <si>
+    <t>用户在小程序排行榜显示有评级，App已登录同一账号</t>
+  </si>
+  <si>
+    <t>1.在小程序查看排行榜，确认某用户显示有评级
+2.打开App登录同一账号
+3.进入排行榜页面
+4.查看同一用户的评级信息
+5.对比两端评级展示</t>
+  </si>
+  <si>
+    <t>1.小程序排行榜正确显示用户评级
+2.App排行榜同一用户也显示评级（非数据不足）
+3.两端评级数据一致
+4.有评级数据的用户在App端不应显示数据不足</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0152</t>
+  </si>
+  <si>
+    <t>视频模块</t>
+  </si>
+  <si>
+    <t>视频制作中断后自动重新制作</t>
+  </si>
+  <si>
+    <t>未离开App时视频制作不被中断，或中断后不自动重新制作</t>
+  </si>
+  <si>
+    <t>用户已登录App，有视频正在下载/制作中</t>
+  </si>
+  <si>
+    <t>1.解锁一个视频，开始下载/制作
+2.保持App在前台不离开
+3.观察视频制作进度
+4.检查视频是否被中断
+5.检查是否出现自动重新制作的情况</t>
+  </si>
+  <si>
+    <t>1.视频正常下载/制作中
+2.App在前台时视频制作流程不被中断
+3.不出现自动重新制作的情况
+4.若确实被中断，需有明确提示而非静默重新制作</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0153</t>
+  </si>
+  <si>
+    <t>卡券模块</t>
+  </si>
+  <si>
+    <t>过期券在App和小程序的显示一致性</t>
+  </si>
+  <si>
+    <t>App和小程序对过期视频券的显示逻辑保持一致</t>
+  </si>
+  <si>
+    <t>用户账号下有过期视频券</t>
+  </si>
+  <si>
+    <t>1.在小程序查看【我的卡券】页面
+2.检查是否显示过期券
+3.打开App登录同一账号
+4.进入【我的卡券】页面
+5.检查是否显示过期券
+6.对比两端过期券的展示逻辑</t>
+  </si>
+  <si>
+    <t>1.小程序和App对过期券的显示逻辑一致
+2.若小程序不显示过期券，App也不应显示
+3.若显示过期券，两端均应有明确的已过期标识
+4.过期券不应误导用户认为仍可使用</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0154</t>
+  </si>
+  <si>
+    <t>视频列表状态与实际一致性</t>
+  </si>
+  <si>
+    <t>视频列表中显示的状态与视频实际状态一致</t>
+  </si>
+  <si>
+    <t>用户已登录App，有多个不同状态的视频</t>
+  </si>
+  <si>
+    <t>1.进入【我的视频】页面
+2.查看各视频卡片的状态标签
+3.点击进入单个视频，查看实际状态
+4.返回列表页对比状态标签
+5.刷新页面后再次检查状态是否更新
+6.对比场视频tab和视频列表的状态</t>
+  </si>
+  <si>
+    <t>1.视频列表状态标签与视频实际状态一致
+2.待下载/下载中/制作中/已完成/制作失败等状态准确对应
+3.刷新后状态及时更新
+4.场视频tab与我的视频页状态一致</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0155</t>
+  </si>
+  <si>
+    <t>交手记录模块</t>
+  </si>
+  <si>
+    <t>交手卡片技术统计数据对比条渲染</t>
+  </si>
+  <si>
+    <t>交手卡片技术统计页面的数据对比长条渲染长度与实际数值成比例</t>
+  </si>
+  <si>
+    <t>用户有交手记录数据，双方各项技术统计数值存在差异</t>
+  </si>
+  <si>
+    <t>1.进入交手记录页面
+2.点击一条交手记录进入详情
+3.查看交手卡片技术统计页面
+4.检查各项数据对比长条（蓝色/绿色进度条）
+5.对比长条渲染长度与对应数值是否成比例
+6.特别关注数值差距大但长条长度差距小的情况</t>
+  </si>
+  <si>
+    <t>1.技术统计页面正常展示
+2.数据对比长条长度与实际数值成比例
+3.数值大的一方长条明显更长
+4.蓝色/绿色进度条渲染正确，无视觉与数据矛盾</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0156</t>
+  </si>
+  <si>
+    <t>工控机模块</t>
+  </si>
+  <si>
+    <t>工控机开机状态App同步显示</t>
+  </si>
+  <si>
+    <t>工控机开机后App正确显示工控机在线状态</t>
+  </si>
+  <si>
+    <t>工控机已开机并联网，App已登录同一账号</t>
+  </si>
+  <si>
+    <t>1.确认工控机已开机
+2.打开App
+3.查看工控机状态显示
+4.等待几分钟后再次查看
+5.对比工控机实际状态与App显示</t>
+  </si>
+  <si>
+    <t>1.App正确显示工控机已开机（在线）状态
+2.状态同步及时，无明显延迟
+3.App显示状态与工控机实际状态一致</t>
+  </si>
+  <si>
     <t>IAP支付解锁视频成功</t>
   </si>
   <si>
@@ -5206,6 +5430,57 @@
 2.Pro Max各页面字体自适应，显示正常
 3.小字号页面字体已调整至可读
 4.自适应异常页面已使用固定字号</t>
+  </si>
+  <si>
+    <t>登录模块</t>
+  </si>
+  <si>
+    <t>Apple账号登录显示昵称和头像</t>
+  </si>
+  <si>
+    <t>使用Apple ID登录后App正确显示用户昵称和头像</t>
+  </si>
+  <si>
+    <t>用户使用Apple ID注册/登录，账号已绑定昵称和头像</t>
+  </si>
+  <si>
+    <t>1.在iOS设备打开App
+2.选择【通过Apple登录】
+3.完成Apple ID授权登录
+4.进入App首页，查看个人卡片
+5.查看个人数据页面头像和昵称</t>
+  </si>
+  <si>
+    <t>1.Apple ID授权登录成功
+2.App首页个人卡片正确显示用户昵称
+3.头像正确显示（非默认头像/空白）
+4.个人数据页面昵称和头像与Apple账号一致</t>
+  </si>
+  <si>
+    <t>扫码登录计分系统后反馈</t>
+  </si>
+  <si>
+    <t>Apple账号登录后扫描计分系统二维码正常反馈登录结果</t>
+  </si>
+  <si>
+    <t>用户已通过Apple ID登录App，计分系统二维码可用</t>
+  </si>
+  <si>
+    <t>1.打开App扫码功能
+2.扫描计分系统管理后台二维码
+3.观察App端反馈
+4.查看计分系统端登录状态</t>
+  </si>
+  <si>
+    <t>1.App扫描后正确识别计分系统二维码
+2.App端给出明确的扫码结果反馈（成功/失败提示）
+3.扫码成功后计分系统端正常登录</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0157</t>
+  </si>
+  <si>
+    <t>斯诺克大师V1.0.1-0158</t>
   </si>
   <si>
     <t>SM-001</t>
@@ -6685,7 +6960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T159"/>
+  <dimension ref="A1:T163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -14238,18 +14513,515 @@
         <v>103</v>
       </c>
     </row>
-    <row r="155" ht="49.5" customHeight="1"/>
-    <row r="156" ht="99" customHeight="1"/>
-    <row r="157" ht="82.5" customHeight="1"/>
-    <row r="158" ht="82.5" customHeight="1"/>
-    <row r="159" ht="33" customHeight="1"/>
+    <row r="155" ht="49.5" customHeight="1" spans="1:20">
+      <c r="A155" s="6" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="156" ht="99" customHeight="1" spans="1:20">
+      <c r="A156" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K156" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L156" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O156" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R156" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T156" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="157" ht="82.5" customHeight="1" spans="1:20">
+      <c r="A157" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K157" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L157" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O157" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R157" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T157" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="158" ht="82.5" customHeight="1" spans="1:20">
+      <c r="A158" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K158" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L158" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O158" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R158" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T158" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="159" ht="33" customHeight="1" spans="1:20">
+      <c r="A159" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K159" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L159" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O159" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R159" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T159" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="160" ht="99" spans="1:20">
+      <c r="A160" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K160" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L160" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O160" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R160" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T160" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="161" ht="99" spans="1:20">
+      <c r="A161" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K161" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L161" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O161" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R161" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T161" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="162" ht="99" spans="1:20">
+      <c r="A162" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K162" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L162" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O162" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R162" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T162" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="163" ht="82.5" spans="1:20">
+      <c r="A163" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K163" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L163" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O163" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R163" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T163" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O159" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O163" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A155:J155"/>
   </mergeCells>
   <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -14305,7 +15077,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T159"/>
+  <dimension ref="A1:T164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -14428,19 +15200,19 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>934</v>
+        <v>989</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>935</v>
+        <v>990</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>936</v>
+        <v>991</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>937</v>
+        <v>992</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>938</v>
+        <v>993</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>30</v>
@@ -14470,19 +15242,19 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>939</v>
+        <v>994</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>940</v>
+        <v>995</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>936</v>
+        <v>991</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>941</v>
+        <v>996</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>942</v>
+        <v>997</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>37</v>
@@ -14512,19 +15284,19 @@
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>943</v>
+        <v>998</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>944</v>
+        <v>999</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>945</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>946</v>
+        <v>1001</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>947</v>
+        <v>1002</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>37</v>
@@ -14554,19 +15326,19 @@
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>948</v>
+        <v>1003</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>949</v>
+        <v>1004</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>950</v>
+        <v>1005</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>951</v>
+        <v>1006</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>952</v>
+        <v>1007</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>30</v>
@@ -14596,19 +15368,19 @@
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>953</v>
+        <v>1008</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>954</v>
+        <v>1009</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>955</v>
+        <v>1010</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>956</v>
+        <v>1011</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>957</v>
+        <v>1012</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>50</v>
@@ -14638,19 +15410,19 @@
         <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>958</v>
+        <v>1013</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>959</v>
+        <v>1014</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>960</v>
+        <v>1015</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>961</v>
+        <v>1016</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>962</v>
+        <v>1017</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>37</v>
@@ -14680,19 +15452,19 @@
         <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>963</v>
+        <v>1018</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>964</v>
+        <v>1019</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>965</v>
+        <v>1020</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>966</v>
+        <v>1021</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>967</v>
+        <v>1022</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>37</v>
@@ -14722,19 +15494,19 @@
         <v>59</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>968</v>
+        <v>1023</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>969</v>
+        <v>1024</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>936</v>
+        <v>991</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>970</v>
+        <v>1025</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>971</v>
+        <v>1026</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>37</v>
@@ -14764,19 +15536,19 @@
         <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>972</v>
+        <v>1027</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>973</v>
+        <v>1028</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>936</v>
+        <v>991</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>974</v>
+        <v>1029</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>975</v>
+        <v>1030</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>50</v>
@@ -14806,19 +15578,19 @@
         <v>72</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>976</v>
+        <v>1031</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>977</v>
+        <v>1032</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>978</v>
+        <v>1033</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>979</v>
+        <v>1034</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>980</v>
+        <v>1035</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>37</v>
@@ -14848,19 +15620,19 @@
         <v>72</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>981</v>
+        <v>1036</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>982</v>
+        <v>1037</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>983</v>
+        <v>1038</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>984</v>
+        <v>1039</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>985</v>
+        <v>1040</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>50</v>
@@ -14890,19 +15662,19 @@
         <v>79</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>986</v>
+        <v>1041</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>987</v>
+        <v>1042</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>950</v>
+        <v>1005</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>988</v>
+        <v>1043</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>989</v>
+        <v>1044</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>50</v>
@@ -14938,13 +15710,13 @@
         <v>93</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>990</v>
+        <v>1045</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>991</v>
+        <v>1046</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>992</v>
+        <v>1047</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>50</v>
@@ -14977,16 +15749,16 @@
         <v>98</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>993</v>
+        <v>1048</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>994</v>
+        <v>1049</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>995</v>
+        <v>1050</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>996</v>
+        <v>1051</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>37</v>
@@ -15036,19 +15808,19 @@
         <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>997</v>
+        <v>1052</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>998</v>
+        <v>1053</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>999</v>
+        <v>1054</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>1000</v>
+        <v>1055</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>1001</v>
+        <v>1056</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>37</v>
@@ -15098,19 +15870,19 @@
         <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1002</v>
+        <v>1057</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1003</v>
+        <v>1058</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>936</v>
+        <v>991</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1004</v>
+        <v>1059</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>1005</v>
+        <v>1060</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>37</v>
@@ -15160,19 +15932,19 @@
         <v>79</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1006</v>
+        <v>1061</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1007</v>
+        <v>1062</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1008</v>
+        <v>1063</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1009</v>
+        <v>1064</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>1010</v>
+        <v>1065</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>50</v>
@@ -15202,19 +15974,19 @@
         <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1011</v>
+        <v>1066</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>1012</v>
+        <v>1067</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>994</v>
+        <v>1049</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>1013</v>
+        <v>1068</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>1014</v>
+        <v>1069</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>37</v>
@@ -15264,19 +16036,19 @@
         <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1015</v>
+        <v>1070</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>129</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1016</v>
+        <v>1071</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>1017</v>
+        <v>1072</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>1018</v>
+        <v>1073</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>37</v>
@@ -15326,19 +16098,19 @@
         <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1019</v>
+        <v>1074</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>1020</v>
+        <v>1075</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>994</v>
+        <v>1049</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1021</v>
+        <v>1076</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>1022</v>
+        <v>1077</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>37</v>
@@ -15391,16 +16163,16 @@
         <v>140</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1023</v>
+        <v>1078</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1024</v>
+        <v>1079</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1025</v>
+        <v>1080</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>1026</v>
+        <v>1081</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>37</v>
@@ -15450,19 +16222,19 @@
         <v>24</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1027</v>
+        <v>1082</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>1028</v>
+        <v>1083</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1029</v>
+        <v>1084</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>1030</v>
+        <v>1085</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>1031</v>
+        <v>1086</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>37</v>
@@ -15512,19 +16284,19 @@
         <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1032</v>
+        <v>1087</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>1033</v>
+        <v>1088</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1034</v>
+        <v>1089</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>1030</v>
+        <v>1085</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>1035</v>
+        <v>1090</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>37</v>
@@ -15574,19 +16346,19 @@
         <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1036</v>
+        <v>1091</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>1037</v>
+        <v>1092</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>1038</v>
+        <v>1093</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>1039</v>
+        <v>1094</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>1040</v>
+        <v>1095</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>37</v>
@@ -15636,19 +16408,19 @@
         <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1041</v>
+        <v>1096</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>1042</v>
+        <v>1097</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1043</v>
+        <v>1098</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1044</v>
+        <v>1099</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>1045</v>
+        <v>1100</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>37</v>
@@ -15698,19 +16470,19 @@
         <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1046</v>
+        <v>1101</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1047</v>
+        <v>1102</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>1048</v>
+        <v>1103</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>1049</v>
+        <v>1104</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>37</v>
@@ -15740,19 +16512,19 @@
         <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1050</v>
+        <v>1105</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>1051</v>
+        <v>1106</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1052</v>
+        <v>1107</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1053</v>
+        <v>1108</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>1054</v>
+        <v>1109</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>37</v>
@@ -15782,19 +16554,19 @@
         <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1055</v>
+        <v>1110</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>1056</v>
+        <v>1111</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>1057</v>
+        <v>1112</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>1058</v>
+        <v>1113</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>50</v>
@@ -15824,16 +16596,16 @@
         <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1059</v>
+        <v>1114</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1060</v>
+        <v>1115</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1052</v>
+        <v>1107</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1061</v>
+        <v>1116</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>231</v>
@@ -15866,19 +16638,19 @@
         <v>24</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1062</v>
+        <v>1117</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>1063</v>
+        <v>1118</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>235</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>1064</v>
+        <v>1119</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>1065</v>
+        <v>1120</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>37</v>
@@ -15908,19 +16680,19 @@
         <v>24</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1066</v>
+        <v>1121</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>1067</v>
+        <v>1122</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>1068</v>
+        <v>1123</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>1069</v>
+        <v>1124</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1070</v>
+        <v>1125</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>37</v>
@@ -15998,13 +16770,13 @@
         <v>257</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>1071</v>
+        <v>1126</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>259</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>1072</v>
+        <v>1127</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>37</v>
@@ -16076,19 +16848,19 @@
         <v>24</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1073</v>
+        <v>1128</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>1074</v>
+        <v>1129</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>1075</v>
+        <v>1130</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>1076</v>
+        <v>1131</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>1077</v>
+        <v>1132</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>37</v>
@@ -16138,19 +16910,19 @@
         <v>24</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1078</v>
+        <v>1133</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>1079</v>
+        <v>1134</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>1080</v>
+        <v>1135</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>1081</v>
+        <v>1136</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>1082</v>
+        <v>1137</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>37</v>
@@ -16200,16 +16972,16 @@
         <v>24</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1083</v>
+        <v>1138</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>1084</v>
+        <v>1139</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>1085</v>
+        <v>1140</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>1086</v>
+        <v>1141</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>296</v>
@@ -16262,19 +17034,19 @@
         <v>24</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1087</v>
+        <v>1142</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>1088</v>
+        <v>1143</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>1089</v>
+        <v>1144</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1090</v>
+        <v>1145</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>1091</v>
+        <v>1146</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>50</v>
@@ -16510,16 +17282,16 @@
         <v>72</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1092</v>
+        <v>1147</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1093</v>
+        <v>1148</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>1094</v>
+        <v>1149</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>1095</v>
+        <v>1150</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>332</v>
@@ -16572,19 +17344,19 @@
         <v>24</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1096</v>
+        <v>1151</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>1097</v>
+        <v>1152</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1098</v>
+        <v>1153</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1099</v>
+        <v>1154</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>1100</v>
+        <v>1155</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>37</v>
@@ -16614,19 +17386,19 @@
         <v>24</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1101</v>
+        <v>1156</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>1102</v>
+        <v>1157</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>1103</v>
+        <v>1158</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>1104</v>
+        <v>1159</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>1105</v>
+        <v>1160</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>37</v>
@@ -16656,19 +17428,19 @@
         <v>24</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1106</v>
+        <v>1161</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>1107</v>
+        <v>1162</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1108</v>
+        <v>1163</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1109</v>
+        <v>1164</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>1110</v>
+        <v>1165</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>37</v>
@@ -16698,19 +17470,19 @@
         <v>24</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1111</v>
+        <v>1166</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1112</v>
+        <v>1167</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>1113</v>
+        <v>1168</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>1114</v>
+        <v>1169</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>1115</v>
+        <v>1170</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>37</v>
@@ -16740,19 +17512,19 @@
         <v>24</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1116</v>
+        <v>1171</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1117</v>
+        <v>1172</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>950</v>
+        <v>1005</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>1118</v>
+        <v>1173</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1119</v>
+        <v>1174</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>50</v>
@@ -16782,19 +17554,19 @@
         <v>24</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1120</v>
+        <v>1175</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1121</v>
+        <v>1176</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>1122</v>
+        <v>1177</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>1123</v>
+        <v>1178</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>1124</v>
+        <v>1179</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>37</v>
@@ -16824,19 +17596,19 @@
         <v>24</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1125</v>
+        <v>1180</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>1126</v>
+        <v>1181</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>1127</v>
+        <v>1182</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>1128</v>
+        <v>1183</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>1129</v>
+        <v>1184</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>37</v>
@@ -16866,19 +17638,19 @@
         <v>24</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1130</v>
+        <v>1185</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>1131</v>
+        <v>1186</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>1132</v>
+        <v>1187</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>1133</v>
+        <v>1188</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>1134</v>
+        <v>1189</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>50</v>
@@ -16908,19 +17680,19 @@
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1135</v>
+        <v>1190</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>1136</v>
+        <v>1191</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>1137</v>
+        <v>1192</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>1138</v>
+        <v>1193</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>1139</v>
+        <v>1194</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>37</v>
@@ -16950,19 +17722,19 @@
         <v>24</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1140</v>
+        <v>1195</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>1141</v>
+        <v>1196</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>1142</v>
+        <v>1197</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>1143</v>
+        <v>1198</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>1144</v>
+        <v>1199</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>37</v>
@@ -16992,19 +17764,19 @@
         <v>24</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1145</v>
+        <v>1200</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>1146</v>
+        <v>1201</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>936</v>
+        <v>991</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>1147</v>
+        <v>1202</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>1148</v>
+        <v>1203</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>50</v>
@@ -17034,19 +17806,19 @@
         <v>24</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1149</v>
+        <v>1204</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>1150</v>
+        <v>1205</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>1151</v>
+        <v>1206</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>1152</v>
+        <v>1207</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>1153</v>
+        <v>1208</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>50</v>
@@ -17076,19 +17848,19 @@
         <v>24</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1154</v>
+        <v>1209</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>1155</v>
+        <v>1210</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>936</v>
+        <v>991</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>1156</v>
+        <v>1211</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>1157</v>
+        <v>1212</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>37</v>
@@ -17118,19 +17890,19 @@
         <v>24</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1158</v>
+        <v>1213</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>1159</v>
+        <v>1214</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>1161</v>
+        <v>1216</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>1162</v>
+        <v>1217</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>50</v>
@@ -17190,7 +17962,7 @@
         <v>337</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>339</v>
@@ -17234,7 +18006,7 @@
         <v>350</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>1164</v>
+        <v>1219</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>352</v>
@@ -17255,7 +18027,7 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
       <c r="T61" s="2" t="s">
-        <v>1165</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="62" ht="54" customHeight="1" spans="1:20">
@@ -17278,7 +18050,7 @@
         <v>357</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>950</v>
+        <v>1005</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>358</v>
@@ -17322,7 +18094,7 @@
         <v>363</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>1166</v>
+        <v>1221</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>365</v>
@@ -17762,7 +18534,7 @@
         <v>430</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>1167</v>
+        <v>1222</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>432</v>
@@ -17783,7 +18555,7 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
       <c r="T73" s="2" t="s">
-        <v>1168</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="74" ht="144" customHeight="1" spans="1:20">
@@ -17848,7 +18620,7 @@
         <v>443</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>1169</v>
+        <v>1224</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>445</v>
@@ -17886,19 +18658,19 @@
         <v>72</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1170</v>
+        <v>1225</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>1171</v>
+        <v>1226</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>1172</v>
+        <v>1227</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>1173</v>
+        <v>1228</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>1174</v>
+        <v>1229</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>37</v>
@@ -17934,7 +18706,7 @@
         <v>462</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>950</v>
+        <v>1005</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>463</v>
@@ -17978,7 +18750,7 @@
         <v>468</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>1175</v>
+        <v>1230</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>470</v>
@@ -17999,7 +18771,7 @@
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
       <c r="T78" s="2" t="s">
-        <v>1176</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="79" ht="54" customHeight="1" spans="1:20">
@@ -18022,7 +18794,7 @@
         <v>475</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>1177</v>
+        <v>1232</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>477</v>
@@ -18043,7 +18815,7 @@
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
       <c r="T79" s="2" t="s">
-        <v>1178</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="80" ht="36" customHeight="1" spans="1:20">
@@ -18066,7 +18838,7 @@
         <v>482</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>1179</v>
+        <v>1234</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>484</v>
@@ -18087,7 +18859,7 @@
       <c r="R80" s="2"/>
       <c r="S80" s="2"/>
       <c r="T80" s="2" t="s">
-        <v>1180</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="81" ht="72" customHeight="1" spans="1:20">
@@ -18110,7 +18882,7 @@
         <v>450</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>1181</v>
+        <v>1236</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>452</v>
@@ -19086,7 +19858,7 @@
         <v>624</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>950</v>
+        <v>1005</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>625</v>
@@ -19166,19 +19938,19 @@
         <v>24</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>1182</v>
+        <v>1237</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>1183</v>
+        <v>1238</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>1184</v>
+        <v>1239</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>1185</v>
+        <v>1240</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>1186</v>
+        <v>1241</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>30</v>
@@ -19211,16 +19983,16 @@
         <v>637</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>1187</v>
+        <v>1242</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>633</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>1188</v>
+        <v>1243</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>1189</v>
+        <v>1244</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>37</v>
@@ -19250,19 +20022,19 @@
         <v>24</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>1190</v>
+        <v>1245</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>1191</v>
+        <v>1246</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>1192</v>
+        <v>1247</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>1193</v>
+        <v>1248</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>1194</v>
+        <v>1249</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>30</v>
@@ -19292,19 +20064,19 @@
         <v>24</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>1195</v>
+        <v>1250</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>1196</v>
+        <v>1251</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>1192</v>
+        <v>1247</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>1197</v>
+        <v>1252</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>1198</v>
+        <v>1253</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>37</v>
@@ -19334,19 +20106,19 @@
         <v>24</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>1199</v>
+        <v>1254</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>1200</v>
+        <v>1255</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>88</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>1201</v>
+        <v>1256</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>1202</v>
+        <v>1257</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>37</v>
@@ -19379,16 +20151,16 @@
         <v>659</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>1203</v>
+        <v>1258</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>88</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>1204</v>
+        <v>1259</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>1205</v>
+        <v>1260</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>37</v>
@@ -19421,16 +20193,16 @@
         <v>665</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>1206</v>
+        <v>1261</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>88</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>1207</v>
+        <v>1262</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>1208</v>
+        <v>1263</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>37</v>
@@ -19463,16 +20235,16 @@
         <v>670</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>1209</v>
+        <v>1264</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>1210</v>
+        <v>1265</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>1211</v>
+        <v>1266</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>1212</v>
+        <v>1267</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>37</v>
@@ -19502,19 +20274,19 @@
         <v>72</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1213</v>
+        <v>1268</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>1214</v>
+        <v>1269</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>1215</v>
+        <v>1270</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>1216</v>
+        <v>1271</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>1217</v>
+        <v>1272</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>37</v>
@@ -19547,16 +20319,16 @@
         <v>688</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>1218</v>
+        <v>1273</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>1219</v>
+        <v>1274</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>1220</v>
+        <v>1275</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>1221</v>
+        <v>1276</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>50</v>
@@ -19595,10 +20367,10 @@
         <v>695</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>1222</v>
+        <v>1277</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>1223</v>
+        <v>1278</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>50</v>
@@ -19631,16 +20403,16 @@
         <v>705</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>1224</v>
+        <v>1279</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>650</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>1225</v>
+        <v>1280</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>1226</v>
+        <v>1281</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>37</v>
@@ -19693,16 +20465,16 @@
         <v>699</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>1227</v>
+        <v>1282</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>1228</v>
+        <v>1283</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>1229</v>
+        <v>1284</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>1230</v>
+        <v>1285</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>37</v>
@@ -20027,16 +20799,16 @@
         <v>735</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>1231</v>
+        <v>1286</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>737</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>1232</v>
+        <v>1287</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>1233</v>
+        <v>1288</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>30</v>
@@ -20095,10 +20867,10 @@
         <v>743</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>1234</v>
+        <v>1289</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>1235</v>
+        <v>1290</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>37</v>
@@ -20131,16 +20903,16 @@
         <v>747</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>1236</v>
+        <v>1291</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>755</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>1237</v>
+        <v>1292</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>1238</v>
+        <v>1293</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>30</v>
@@ -20170,19 +20942,19 @@
         <v>24</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>1239</v>
+        <v>1294</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>1240</v>
+        <v>1295</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>1241</v>
+        <v>1296</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>1242</v>
+        <v>1297</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>1243</v>
+        <v>1298</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>37</v>
@@ -20241,10 +21013,10 @@
         <v>834</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>1244</v>
+        <v>1299</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>1245</v>
+        <v>1300</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>37</v>
@@ -20300,10 +21072,10 @@
         <v>827</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>1246</v>
+        <v>1301</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>1247</v>
+        <v>1302</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>830</v>
@@ -20365,10 +21137,10 @@
         <v>834</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>1248</v>
+        <v>1303</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>1249</v>
+        <v>1304</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>37</v>
@@ -20424,13 +21196,13 @@
         <v>845</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>1250</v>
+        <v>1305</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>847</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>1251</v>
+        <v>1306</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>30</v>
@@ -20492,7 +21264,7 @@
         <v>853</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>1252</v>
+        <v>1307</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>30</v>
@@ -20554,7 +21326,7 @@
         <v>859</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>1253</v>
+        <v>1308</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>30</v>
@@ -20607,16 +21379,16 @@
         <v>759</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>1254</v>
+        <v>1309</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>1255</v>
+        <v>1310</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>1256</v>
+        <v>1311</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>1257</v>
+        <v>1312</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>30</v>
@@ -20652,7 +21424,7 @@
         <v>863</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>1258</v>
+        <v>1313</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>865</v>
@@ -20708,19 +21480,19 @@
         <v>24</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>1259</v>
+        <v>1314</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>1260</v>
+        <v>1315</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>1261</v>
+        <v>1316</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>1262</v>
+        <v>1317</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>1263</v>
+        <v>1318</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>50</v>
@@ -20770,19 +21542,19 @@
         <v>24</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>1264</v>
+        <v>1319</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>1265</v>
+        <v>1320</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>1266</v>
+        <v>1321</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>1267</v>
+        <v>1322</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>1268</v>
+        <v>1323</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>50</v>
@@ -20832,19 +21604,19 @@
         <v>24</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>1269</v>
+        <v>1324</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>1271</v>
+        <v>1326</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>1272</v>
+        <v>1327</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>1273</v>
+        <v>1328</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>37</v>
@@ -20897,16 +21669,16 @@
         <v>796</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>1274</v>
+        <v>1329</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>1275</v>
+        <v>1330</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>1276</v>
+        <v>1331</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>1277</v>
+        <v>1332</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>37</v>
@@ -20959,16 +21731,16 @@
         <v>802</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>1278</v>
+        <v>1333</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>1279</v>
+        <v>1334</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>1280</v>
+        <v>1335</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>1281</v>
+        <v>1336</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>37</v>
@@ -21021,16 +21793,16 @@
         <v>808</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>1282</v>
+        <v>1337</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>1283</v>
+        <v>1338</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>1284</v>
+        <v>1339</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>1285</v>
+        <v>1340</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>50</v>
@@ -21063,16 +21835,16 @@
         <v>814</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>1286</v>
+        <v>1341</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>1287</v>
+        <v>1342</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>1288</v>
+        <v>1343</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>1289</v>
+        <v>1344</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>30</v>
@@ -21125,13 +21897,13 @@
         <v>874</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>1290</v>
+        <v>1345</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>834</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>1291</v>
+        <v>1346</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>877</v>
@@ -21258,7 +22030,7 @@
         <v>888</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>1292</v>
+        <v>1347</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>37</v>
@@ -21332,19 +22104,19 @@
         <v>24</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>1293</v>
+        <v>1348</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>1294</v>
+        <v>1349</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>1295</v>
+        <v>1350</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>1296</v>
+        <v>1351</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>1297</v>
+        <v>1352</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>37</v>
@@ -21459,16 +22231,16 @@
         <v>917</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>1298</v>
+        <v>1353</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>1299</v>
+        <v>1354</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>1300</v>
+        <v>1355</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>1301</v>
+        <v>1356</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>37</v>
@@ -21521,16 +22293,16 @@
         <v>905</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>1302</v>
+        <v>1357</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>1303</v>
+        <v>1358</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>1304</v>
+        <v>1359</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>1305</v>
+        <v>1360</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>50</v>
@@ -21732,15 +22504,635 @@
         <v>103</v>
       </c>
     </row>
-    <row r="154" ht="49.5" customHeight="1"/>
-    <row r="155" ht="82.5" customHeight="1"/>
-    <row r="156" ht="49.5" customHeight="1"/>
-    <row r="157" ht="49.5" customHeight="1"/>
-    <row r="158" ht="33" customHeight="1"/>
-    <row r="159" ht="66" customHeight="1"/>
+    <row r="154" ht="49.5" customHeight="1" spans="1:20">
+      <c r="A154" s="6" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="155" ht="82.5" customHeight="1" spans="1:20">
+      <c r="A155" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K155" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L155" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M155" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N155" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O155" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P155" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q155" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R155" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S155" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T155" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="156" ht="49.5" customHeight="1" spans="1:20">
+      <c r="A156" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K156" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L156" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O156" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R156" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S156" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T156" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="157" ht="49.5" customHeight="1" spans="1:20">
+      <c r="A157" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K157" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L157" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O157" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R157" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S157" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T157" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="158" ht="33" customHeight="1" spans="1:20">
+      <c r="A158" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K158" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L158" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O158" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R158" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S158" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T158" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="159" ht="66" customHeight="1" spans="1:20">
+      <c r="A159" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K159" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L159" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O159" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R159" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T159" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="160" ht="82.5" spans="1:20">
+      <c r="A160" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K160" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L160" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O160" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R160" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S160" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T160" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="161" ht="99" spans="1:20">
+      <c r="A161" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K161" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L161" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O161" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R161" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S161" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T161" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="162" ht="99" spans="1:20">
+      <c r="A162" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K162" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L162" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O162" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R162" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S162" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T162" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="163" ht="99" spans="1:20">
+      <c r="A163" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K163" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L163" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O163" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R163" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S163" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T163" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="164" ht="82.5" spans="1:20">
+      <c r="A164" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K164" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L164" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M164" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N164" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O164" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P164" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q164" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R164" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="S164" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T164" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A154:J154"/>
   </mergeCells>
   <conditionalFormatting sqref="K2:K10000">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
@@ -21872,31 +23264,31 @@
     </row>
     <row r="2" ht="234" customHeight="1" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>1306</v>
+        <v>1374</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1307</v>
+        <v>1375</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1308</v>
+        <v>1376</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1309</v>
+        <v>1377</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1310</v>
+        <v>1378</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>1311</v>
+        <v>1379</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1312</v>
+        <v>1380</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>30</v>
@@ -21914,31 +23306,31 @@
     </row>
     <row r="3" ht="252" customHeight="1" spans="1:20">
       <c r="A3" s="2" t="s">
-        <v>1313</v>
+        <v>1381</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1307</v>
+        <v>1375</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1314</v>
+        <v>1382</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1315</v>
+        <v>1383</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1316</v>
+        <v>1384</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1317</v>
+        <v>1385</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1318</v>
+        <v>1386</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>30</v>
@@ -21956,31 +23348,31 @@
     </row>
     <row r="4" ht="234" customHeight="1" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>1319</v>
+        <v>1387</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1307</v>
+        <v>1375</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1320</v>
+        <v>1388</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1321</v>
+        <v>1389</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1322</v>
+        <v>1390</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1323</v>
+        <v>1391</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1324</v>
+        <v>1392</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>30</v>
@@ -21998,31 +23390,31 @@
     </row>
     <row r="5" ht="409.5" customHeight="1" spans="1:20">
       <c r="A5" s="2" t="s">
-        <v>1325</v>
+        <v>1393</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1307</v>
+        <v>1375</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1326</v>
+        <v>1394</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1327</v>
+        <v>1395</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>338</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1328</v>
+        <v>1396</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>1329</v>
+        <v>1397</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>30</v>
@@ -22040,31 +23432,31 @@
     </row>
     <row r="6" ht="162" customHeight="1" spans="1:20">
       <c r="A6" s="2" t="s">
-        <v>1330</v>
+        <v>1398</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1307</v>
+        <v>1375</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1331</v>
+        <v>1399</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1332</v>
+        <v>1400</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1333</v>
+        <v>1401</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1334</v>
+        <v>1402</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>1335</v>
+        <v>1403</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>30</v>
@@ -22082,31 +23474,31 @@
     </row>
     <row r="7" ht="216" customHeight="1" spans="1:20">
       <c r="A7" s="4" t="s">
-        <v>1336</v>
+        <v>1404</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1307</v>
+        <v>1375</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1337</v>
+        <v>1405</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1338</v>
+        <v>1406</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>1339</v>
+        <v>1407</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>1340</v>
+        <v>1408</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>1341</v>
+        <v>1409</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>30</v>
@@ -22124,31 +23516,31 @@
     </row>
     <row r="8" ht="198" customHeight="1" spans="1:20">
       <c r="A8" s="4" t="s">
-        <v>1342</v>
+        <v>1410</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1307</v>
+        <v>1375</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1343</v>
+        <v>1411</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1343</v>
+        <v>1411</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1344</v>
+        <v>1412</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>1345</v>
+        <v>1413</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>1346</v>
+        <v>1414</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>1347</v>
+        <v>1415</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>30</v>
